--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_run_10/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="520">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,772 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.5672,0.3656,0.0753,0.0018</t>
-  </si>
-  <si>
-    <t>0.7387,0.2040,0.0786,0.0030</t>
-  </si>
-  <si>
-    <t>0.5065,0.4564,0.0841,0.0016</t>
-  </si>
-  <si>
-    <t>0.8504,0.1001,0.0619,0.0021</t>
-  </si>
-  <si>
-    <t>0.5166,0.4579,0.0870,0.0014</t>
-  </si>
-  <si>
-    <t>0.6413,0.3373,0.0930,0.0050</t>
-  </si>
-  <si>
-    <t>0.5911,0.3870,0.0820,0.0027</t>
-  </si>
-  <si>
-    <t>0.6470,0.3649,0.0814,0.0029</t>
-  </si>
-  <si>
-    <t>0.3870,0.6403,0.0616,0.0017</t>
-  </si>
-  <si>
-    <t>0.6722,0.3823,0.0344,0.0005</t>
-  </si>
-  <si>
-    <t>0.7047,0.3021,0.0793,0.0035</t>
-  </si>
-  <si>
-    <t>0.7306,0.3340,0.0279,0.0004</t>
-  </si>
-  <si>
-    <t>0.6136,0.4272,0.0522,0.0014</t>
-  </si>
-  <si>
-    <t>0.7087,0.2930,0.0374,0.0004</t>
-  </si>
-  <si>
-    <t>0.8037,0.2727,0.0099,0.0001</t>
-  </si>
-  <si>
-    <t>0.8581,0.1129,0.0297,0.0002</t>
-  </si>
-  <si>
-    <t>0.5604,0.4421,0.0402,0.0004</t>
-  </si>
-  <si>
-    <t>0.1623,0.8107,0.0664,0.0008</t>
-  </si>
-  <si>
-    <t>0.2191,0.7880,0.0500,0.0006</t>
-  </si>
-  <si>
-    <t>0.1664,0.8382,0.0480,0.0008</t>
-  </si>
-  <si>
-    <t>0.0524,0.9550,0.0179,0.0002</t>
-  </si>
-  <si>
-    <t>0.1393,0.8881,0.0255,0.0002</t>
-  </si>
-  <si>
-    <t>0.8584,0.1302,0.0403,0.0004</t>
-  </si>
-  <si>
-    <t>0.6777,0.3379,0.0332,0.0003</t>
-  </si>
-  <si>
-    <t>0.6473,0.3519,0.0486,0.0008</t>
-  </si>
-  <si>
-    <t>0.5578,0.4127,0.0423,0.0003</t>
-  </si>
-  <si>
-    <t>0.8490,0.0881,0.0705,0.0006</t>
-  </si>
-  <si>
-    <t>0.7999,0.1139,0.0599,0.0004</t>
-  </si>
-  <si>
-    <t>0.7952,0.0511,0.1822,0.0011</t>
-  </si>
-  <si>
-    <t>0.4894,0.5797,0.0230,0.0002</t>
-  </si>
-  <si>
-    <t>0.5995,0.4377,0.0341,0.0005</t>
-  </si>
-  <si>
-    <t>0.1750,0.3367,0.6809,0.0017</t>
-  </si>
-  <si>
-    <t>0.2049,0.7561,0.0735,0.0006</t>
-  </si>
-  <si>
-    <t>0.6998,0.3558,0.0335,0.0007</t>
-  </si>
-  <si>
-    <t>0.5469,0.3713,0.0921,0.0019</t>
-  </si>
-  <si>
-    <t>0.2093,0.8093,0.0583,0.0010</t>
-  </si>
-  <si>
-    <t>0.2634,0.8054,0.0220,0.0001</t>
-  </si>
-  <si>
-    <t>0.5118,0.3659,0.2072,0.0015</t>
-  </si>
-  <si>
-    <t>0.8899,0.0267,0.1501,0.0018</t>
-  </si>
-  <si>
-    <t>0.8065,0.0783,0.1325,0.0035</t>
-  </si>
-  <si>
-    <t>0.8809,0.0577,0.0731,0.0008</t>
-  </si>
-  <si>
-    <t>0.7787,0.0981,0.1117,0.0005</t>
-  </si>
-  <si>
-    <t>0.2141,0.8047,0.0511,0.0002</t>
-  </si>
-  <si>
-    <t>0.0962,0.8574,0.1185,0.0005</t>
-  </si>
-  <si>
-    <t>0.5486,0.4226,0.0589,0.0010</t>
-  </si>
-  <si>
-    <t>0.1512,0.8559,0.0414,0.0004</t>
-  </si>
-  <si>
-    <t>0.1126,0.9175,0.0206,0.0002</t>
-  </si>
-  <si>
-    <t>0.1593,0.8848,0.0237,0.0002</t>
-  </si>
-  <si>
-    <t>0.6782,0.0383,0.5608,0.0014</t>
-  </si>
-  <si>
-    <t>0.5964,0.1893,0.2701,0.0019</t>
-  </si>
-  <si>
-    <t>0.8710,0.0744,0.0503,0.0002</t>
-  </si>
-  <si>
-    <t>0.4184,0.1838,0.4405,0.0048</t>
-  </si>
-  <si>
-    <t>0.3588,0.3344,0.3367,0.0010</t>
-  </si>
-  <si>
-    <t>0.7698,0.1223,0.0717,0.0002</t>
-  </si>
-  <si>
-    <t>0.4726,0.5356,0.0539,0.0013</t>
-  </si>
-  <si>
-    <t>0.3349,0.6743,0.0832,0.0017</t>
-  </si>
-  <si>
-    <t>0.5248,0.5074,0.0595,0.0021</t>
-  </si>
-  <si>
-    <t>0.4582,0.3970,0.2198,0.0041</t>
-  </si>
-  <si>
-    <t>0.7064,0.3165,0.0450,0.0010</t>
-  </si>
-  <si>
-    <t>0.5835,0.4153,0.0946,0.0042</t>
-  </si>
-  <si>
-    <t>0.2938,0.7101,0.0808,0.0021</t>
-  </si>
-  <si>
-    <t>0.0912,0.6279,0.6166,0.0012</t>
-  </si>
-  <si>
-    <t>0.2024,0.5308,0.5593,0.0046</t>
-  </si>
-  <si>
-    <t>0.8198,0.0406,0.1944,0.0008</t>
-  </si>
-  <si>
-    <t>0.0591,0.7765,0.5687,0.0007</t>
-  </si>
-  <si>
-    <t>0.5909,0.0514,0.5373,0.0012</t>
-  </si>
-  <si>
-    <t>0.6484,0.4809,0.0180,0.0002</t>
-  </si>
-  <si>
-    <t>0.0853,0.9286,0.0225,0.0001</t>
-  </si>
-  <si>
-    <t>0.6907,0.3644,0.0229,0.0003</t>
-  </si>
-  <si>
-    <t>0.7092,0.3985,0.0214,0.0002</t>
-  </si>
-  <si>
-    <t>0.0449,0.9024,0.1326,0.0004</t>
-  </si>
-  <si>
-    <t>0.1165,0.7176,0.3190,0.0006</t>
-  </si>
-  <si>
-    <t>0.2946,0.4842,0.2435,0.0005</t>
-  </si>
-  <si>
-    <t>0.0949,0.7754,0.2630,0.0005</t>
-  </si>
-  <si>
-    <t>0.0472,0.8880,0.2642,0.0001</t>
-  </si>
-  <si>
-    <t>0.8206,0.1126,0.0794,0.0015</t>
-  </si>
-  <si>
-    <t>0.5764,0.3633,0.0962,0.0105</t>
-  </si>
-  <si>
-    <t>0.8325,0.0932,0.0770,0.0029</t>
-  </si>
-  <si>
-    <t>0.7982,0.1696,0.0600,0.0018</t>
-  </si>
-  <si>
-    <t>0.8423,0.1068,0.0549,0.0010</t>
-  </si>
-  <si>
-    <t>0.7472,0.1634,0.0826,0.0029</t>
-  </si>
-  <si>
-    <t>0.0153,0.9183,0.6826,0.0003</t>
-  </si>
-  <si>
-    <t>0.0525,0.7655,0.6138,0.0009</t>
-  </si>
-  <si>
-    <t>0.1812,0.6339,0.3039,0.0007</t>
-  </si>
-  <si>
-    <t>0.2878,0.4530,0.3410,0.0013</t>
-  </si>
-  <si>
-    <t>0.0499,0.7406,0.6117,0.0004</t>
-  </si>
-  <si>
-    <t>0.1628,0.5957,0.3601,0.0006</t>
-  </si>
-  <si>
-    <t>0.6651,0.3386,0.0595,0.0012</t>
-  </si>
-  <si>
-    <t>0.5318,0.4203,0.0900,0.0026</t>
-  </si>
-  <si>
-    <t>0.3916,0.6277,0.0652,0.0010</t>
-  </si>
-  <si>
-    <t>0.4858,0.5738,0.0366,0.0006</t>
-  </si>
-  <si>
-    <t>0.4692,0.5640,0.0706,0.0014</t>
-  </si>
-  <si>
-    <t>0.4787,0.5459,0.0593,0.0016</t>
-  </si>
-  <si>
-    <t>0.4358,0.5736,0.0792,0.0033</t>
-  </si>
-  <si>
-    <t>0.3759,0.5624,0.0882,0.0007</t>
-  </si>
-  <si>
-    <t>0.6072,0.3674,0.0683,0.0023</t>
-  </si>
-  <si>
-    <t>0.4208,0.5950,0.0693,0.0010</t>
-  </si>
-  <si>
-    <t>0.5020,0.5911,0.0319,0.0006</t>
-  </si>
-  <si>
-    <t>0.5639,0.4951,0.0533,0.0013</t>
-  </si>
-  <si>
-    <t>0.4555,0.5240,0.0817,0.0015</t>
-  </si>
-  <si>
-    <t>0.4295,0.6503,0.0472,0.0011</t>
-  </si>
-  <si>
-    <t>0.4868,0.4932,0.0956,0.0025</t>
-  </si>
-  <si>
-    <t>0.6696,0.3396,0.0673,0.0035</t>
-  </si>
-  <si>
-    <t>0.3385,0.2766,0.5082,0.0044</t>
-  </si>
-  <si>
-    <t>0.6150,0.3264,0.0531,0.0004</t>
-  </si>
-  <si>
-    <t>0.5759,0.3345,0.1097,0.0018</t>
-  </si>
-  <si>
-    <t>0.8415,0.1304,0.0513,0.0009</t>
-  </si>
-  <si>
-    <t>0.0620,0.9359,0.0285,0.0004</t>
-  </si>
-  <si>
-    <t>0.2048,0.8328,0.0266,0.0004</t>
-  </si>
-  <si>
-    <t>0.2026,0.8477,0.0208,0.0004</t>
-  </si>
-  <si>
-    <t>0.3485,0.6244,0.0790,0.0012</t>
-  </si>
-  <si>
-    <t>0.1116,0.8757,0.0512,0.0021</t>
-  </si>
-  <si>
-    <t>0.0474,0.9445,0.0310,0.0003</t>
-  </si>
-  <si>
-    <t>0.2719,0.7239,0.0796,0.0012</t>
-  </si>
-  <si>
-    <t>0.4931,0.5093,0.0374,0.0004</t>
-  </si>
-  <si>
-    <t>0.5063,0.3281,0.1546,0.0015</t>
-  </si>
-  <si>
-    <t>0.4286,0.5600,0.0566,0.0004</t>
-  </si>
-  <si>
-    <t>0.5888,0.3784,0.0485,0.0004</t>
-  </si>
-  <si>
-    <t>0.8045,0.1586,0.0425,0.0005</t>
-  </si>
-  <si>
-    <t>0.2707,0.8005,0.0222,0.0002</t>
-  </si>
-  <si>
-    <t>0.1410,0.8558,0.0458,0.0003</t>
-  </si>
-  <si>
-    <t>0.3692,0.6941,0.0262,0.0003</t>
-  </si>
-  <si>
-    <t>0.2281,0.7964,0.0324,0.0002</t>
-  </si>
-  <si>
-    <t>0.2586,0.7572,0.0428,0.0003</t>
-  </si>
-  <si>
-    <t>0.3663,0.6229,0.0756,0.0011</t>
-  </si>
-  <si>
-    <t>0.2436,0.7702,0.0664,0.0006</t>
-  </si>
-  <si>
-    <t>0.7692,0.3514,0.0168,0.0003</t>
-  </si>
-  <si>
-    <t>0.6469,0.3975,0.0423,0.0011</t>
-  </si>
-  <si>
-    <t>0.4854,0.5325,0.0840,0.0033</t>
-  </si>
-  <si>
-    <t>0.7377,0.3097,0.0309,0.0006</t>
-  </si>
-  <si>
-    <t>0.6136,0.4130,0.0410,0.0004</t>
-  </si>
-  <si>
-    <t>0.8125,0.2563,0.0171,0.0003</t>
-  </si>
-  <si>
-    <t>0.6676,0.3693,0.0375,0.0006</t>
-  </si>
-  <si>
-    <t>0.5176,0.5188,0.0605,0.0013</t>
-  </si>
-  <si>
-    <t>0.1729,0.5911,0.2829,0.0003</t>
-  </si>
-  <si>
-    <t>0.1210,0.5932,0.5418,0.0012</t>
-  </si>
-  <si>
-    <t>0.1194,0.7130,0.3866,0.0018</t>
-  </si>
-  <si>
-    <t>0.4849,0.4176,0.1812,0.0033</t>
-  </si>
-  <si>
-    <t>0.3654,0.6704,0.0603,0.0015</t>
-  </si>
-  <si>
-    <t>0.5267,0.3947,0.0647,0.0006</t>
-  </si>
-  <si>
-    <t>0.6526,0.2336,0.0998,0.0012</t>
-  </si>
-  <si>
-    <t>0.4841,0.4780,0.0697,0.0011</t>
-  </si>
-  <si>
-    <t>0.8902,0.0904,0.0385,0.0008</t>
-  </si>
-  <si>
-    <t>0.8806,0.0583,0.0667,0.0021</t>
-  </si>
-  <si>
-    <t>0.7102,0.1990,0.1011,0.0026</t>
-  </si>
-  <si>
-    <t>0.7469,0.1665,0.1186,0.0046</t>
-  </si>
-  <si>
-    <t>0.4552,0.3717,0.2292,0.0012</t>
-  </si>
-  <si>
-    <t>0.2670,0.7560,0.0612,0.0014</t>
-  </si>
-  <si>
-    <t>0.5607,0.4215,0.0658,0.0014</t>
-  </si>
-  <si>
-    <t>0.4285,0.5749,0.0753,0.0026</t>
-  </si>
-  <si>
-    <t>0.3132,0.7109,0.0513,0.0006</t>
-  </si>
-  <si>
-    <t>0.5065,0.4341,0.1102,0.0031</t>
-  </si>
-  <si>
-    <t>0.5995,0.3897,0.0856,0.0042</t>
-  </si>
-  <si>
-    <t>0.4744,0.5858,0.0571,0.0016</t>
-  </si>
-  <si>
-    <t>0.4881,0.2926,0.3641,0.0150</t>
-  </si>
-  <si>
-    <t>0.5851,0.4396,0.0527,0.0012</t>
-  </si>
-  <si>
-    <t>0.6902,0.2353,0.1106,0.0035</t>
-  </si>
-  <si>
-    <t>0.3793,0.6220,0.0434,0.0006</t>
-  </si>
-  <si>
-    <t>0.5869,0.4825,0.0361,0.0007</t>
-  </si>
-  <si>
-    <t>0.4043,0.5970,0.0446,0.0004</t>
-  </si>
-  <si>
-    <t>0.4874,0.5640,0.0314,0.0008</t>
-  </si>
-  <si>
-    <t>0.4922,0.5413,0.0445,0.0006</t>
-  </si>
-  <si>
-    <t>0.6592,0.3909,0.0292,0.0003</t>
-  </si>
-  <si>
-    <t>0.3736,0.6899,0.0589,0.0013</t>
-  </si>
-  <si>
-    <t>0.6552,0.2850,0.0810,0.0020</t>
-  </si>
-  <si>
-    <t>0.2712,0.7174,0.1048,0.0024</t>
-  </si>
-  <si>
-    <t>0.6613,0.2987,0.0611,0.0012</t>
-  </si>
-  <si>
-    <t>0.5617,0.4883,0.0605,0.0018</t>
-  </si>
-  <si>
-    <t>0.5600,0.5089,0.0415,0.0013</t>
-  </si>
-  <si>
-    <t>0.5138,0.5139,0.0629,0.0015</t>
-  </si>
-  <si>
-    <t>0.3505,0.5926,0.1472,0.0060</t>
-  </si>
-  <si>
-    <t>0.1477,0.9045,0.0191,0.0002</t>
-  </si>
-  <si>
-    <t>0.2386,0.7599,0.0664,0.0010</t>
-  </si>
-  <si>
-    <t>0.2730,0.6792,0.0932,0.0020</t>
-  </si>
-  <si>
-    <t>0.4936,0.6174,0.0241,0.0006</t>
-  </si>
-  <si>
-    <t>0.3608,0.6947,0.0401,0.0008</t>
-  </si>
-  <si>
-    <t>0.4685,0.4767,0.1054,0.0026</t>
-  </si>
-  <si>
-    <t>0.3887,0.6276,0.0670,0.0011</t>
-  </si>
-  <si>
-    <t>0.4870,0.5225,0.0696,0.0023</t>
-  </si>
-  <si>
-    <t>0.0201,0.6978,0.7920,0.0013</t>
-  </si>
-  <si>
-    <t>0.1825,0.8021,0.0763,0.0013</t>
-  </si>
-  <si>
-    <t>0.1828,0.4852,0.3902,0.0012</t>
-  </si>
-  <si>
-    <t>0.5947,0.2582,0.1374,0.0013</t>
-  </si>
-  <si>
-    <t>0.6280,0.1783,0.1585,0.0009</t>
-  </si>
-  <si>
-    <t>0.7191,0.1037,0.2953,0.0009</t>
-  </si>
-  <si>
-    <t>0.5331,0.3342,0.1001,0.0005</t>
-  </si>
-  <si>
-    <t>0.6648,0.3009,0.0379,0.0004</t>
-  </si>
-  <si>
-    <t>0.5319,0.3659,0.0934,0.0009</t>
-  </si>
-  <si>
-    <t>0.8211,0.1262,0.0514,0.0004</t>
-  </si>
-  <si>
-    <t>0.6409,0.3907,0.0266,0.0002</t>
-  </si>
-  <si>
-    <t>0.5508,0.4589,0.0432,0.0005</t>
-  </si>
-  <si>
-    <t>0.4735,0.5025,0.0553,0.0004</t>
-  </si>
-  <si>
-    <t>0.8186,0.1379,0.0655,0.0010</t>
-  </si>
-  <si>
-    <t>0.2979,0.6599,0.0713,0.0008</t>
-  </si>
-  <si>
-    <t>0.7024,0.2929,0.0411,0.0005</t>
-  </si>
-  <si>
-    <t>0.5327,0.5041,0.0309,0.0003</t>
-  </si>
-  <si>
-    <t>0.2366,0.7847,0.0568,0.0008</t>
-  </si>
-  <si>
-    <t>0.2891,0.6171,0.1334,0.0021</t>
-  </si>
-  <si>
-    <t>0.1771,0.8332,0.0566,0.0008</t>
-  </si>
-  <si>
-    <t>0.3923,0.6403,0.0694,0.0017</t>
-  </si>
-  <si>
-    <t>0.5024,0.4801,0.0586,0.0011</t>
-  </si>
-  <si>
-    <t>0.5361,0.4835,0.0352,0.0003</t>
-  </si>
-  <si>
-    <t>0.8688,0.1398,0.0210,0.0003</t>
-  </si>
-  <si>
-    <t>0.7339,0.1875,0.0960,0.0028</t>
-  </si>
-  <si>
-    <t>0.7560,0.1624,0.0665,0.0009</t>
-  </si>
-  <si>
-    <t>0.5291,0.4135,0.0762,0.0014</t>
-  </si>
-  <si>
-    <t>0.7860,0.1606,0.0574,0.0009</t>
-  </si>
-  <si>
-    <t>0.6395,0.3478,0.0568,0.0005</t>
-  </si>
-  <si>
-    <t>0.6424,0.2778,0.1364,0.0013</t>
-  </si>
-  <si>
-    <t>0.7482,0.1161,0.1565,0.0005</t>
-  </si>
-  <si>
-    <t>0.4150,0.1544,0.5171,0.0021</t>
-  </si>
-  <si>
-    <t>0.3799,0.6949,0.0494,0.0016</t>
-  </si>
-  <si>
-    <t>0.3920,0.6233,0.0841,0.0019</t>
-  </si>
-  <si>
-    <t>0.4225,0.5807,0.0891,0.0029</t>
-  </si>
-  <si>
-    <t>0.4040,0.6214,0.0779,0.0021</t>
-  </si>
-  <si>
-    <t>0.5264,0.4748,0.0893,0.0037</t>
-  </si>
-  <si>
-    <t>0.5539,0.5110,0.0433,0.0007</t>
-  </si>
-  <si>
-    <t>0.4957,0.5558,0.0522,0.0013</t>
-  </si>
-  <si>
-    <t>0.4740,0.6203,0.0317,0.0004</t>
-  </si>
-  <si>
-    <t>0.3699,0.4580,0.2188,0.0047</t>
-  </si>
-  <si>
-    <t>0.4309,0.5809,0.0423,0.0005</t>
-  </si>
-  <si>
-    <t>0.6691,0.3069,0.0486,0.0004</t>
-  </si>
-  <si>
-    <t>0.2873,0.4374,0.3156,0.0010</t>
-  </si>
-  <si>
-    <t>0.1951,0.4710,0.5089,0.0019</t>
-  </si>
-  <si>
-    <t>0.3118,0.3983,0.2992,0.0008</t>
-  </si>
-  <si>
-    <t>0.0766,0.4783,0.7174,0.0003</t>
-  </si>
-  <si>
-    <t>0.7123,0.0923,0.2027,0.0009</t>
-  </si>
-  <si>
-    <t>0.0768,0.3244,0.8893,0.0014</t>
-  </si>
-  <si>
-    <t>0.6784,0.2044,0.0948,0.0004</t>
-  </si>
-  <si>
-    <t>0.2693,0.6467,0.1145,0.0007</t>
-  </si>
-  <si>
-    <t>0.7917,0.1546,0.0668,0.0010</t>
-  </si>
-  <si>
-    <t>0.7831,0.1025,0.1053,0.0010</t>
-  </si>
-  <si>
-    <t>0.6939,0.2746,0.0567,0.0007</t>
-  </si>
-  <si>
-    <t>0.5259,0.5049,0.0588,0.0013</t>
-  </si>
-  <si>
-    <t>0.2482,0.7135,0.1159,0.0025</t>
-  </si>
-  <si>
-    <t>0.4285,0.6244,0.0516,0.0011</t>
-  </si>
-  <si>
-    <t>0.4901,0.4761,0.1046,0.0037</t>
-  </si>
-  <si>
-    <t>0.5038,0.5835,0.0355,0.0008</t>
-  </si>
-  <si>
-    <t>0.5304,0.4958,0.0562,0.0018</t>
-  </si>
-  <si>
-    <t>0.4974,0.4667,0.1140,0.0047</t>
-  </si>
-  <si>
-    <t>0.7262,0.2907,0.0437,0.0010</t>
-  </si>
-  <si>
-    <t>0.4170,0.4066,0.1466,0.0003</t>
-  </si>
-  <si>
-    <t>0.2328,0.3435,0.4445,0.0005</t>
-  </si>
-  <si>
-    <t>0.2281,0.5069,0.2486,0.0005</t>
-  </si>
-  <si>
-    <t>0.5820,0.3558,0.0592,0.0005</t>
-  </si>
-  <si>
-    <t>0.6056,0.2525,0.0999,0.0003</t>
-  </si>
-  <si>
-    <t>0.8312,0.0897,0.0992,0.0023</t>
-  </si>
-  <si>
-    <t>0.6400,0.2368,0.0857,0.0011</t>
-  </si>
-  <si>
-    <t>0.5950,0.1910,0.2809,0.0032</t>
-  </si>
-  <si>
-    <t>0.4861,0.4854,0.0781,0.0021</t>
-  </si>
-  <si>
-    <t>0.8102,0.0825,0.1029,0.0025</t>
-  </si>
-  <si>
-    <t>0.8521,0.1311,0.0308,0.0006</t>
-  </si>
-  <si>
-    <t>0.8972,0.0517,0.0712,0.0010</t>
-  </si>
-  <si>
-    <t>0.8801,0.0608,0.0562,0.0013</t>
-  </si>
-  <si>
-    <t>0.6356,0.3154,0.0612,0.0007</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.2092,0.5037,0.0156,0.5010</t>
+  </si>
+  <si>
+    <t>0.0422,0.0017,0.0007,0.9825</t>
+  </si>
+  <si>
+    <t>0.4417,0.0111,0.0239,0.6070</t>
+  </si>
+  <si>
+    <t>0.4815,0.0019,0.0026,0.7143</t>
+  </si>
+  <si>
+    <t>0.9948,0.0031,0.0014,0.0009</t>
+  </si>
+  <si>
+    <t>0.9952,0.0033,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9887,0.0044,0.0046,0.0027</t>
+  </si>
+  <si>
+    <t>0.9972,0.0012,0.0011,0.0006</t>
+  </si>
+  <si>
+    <t>0.9739,0.0183,0.0066,0.0062</t>
+  </si>
+  <si>
+    <t>0.9884,0.0101,0.0021,0.0012</t>
+  </si>
+  <si>
+    <t>0.9926,0.0036,0.0010,0.0019</t>
+  </si>
+  <si>
+    <t>0.9936,0.0068,0.0014,0.0003</t>
+  </si>
+  <si>
+    <t>0.7664,0.0392,0.2679,0.0073</t>
+  </si>
+  <si>
+    <t>0.3773,0.0352,0.7072,0.0115</t>
+  </si>
+  <si>
+    <t>0.8288,0.0462,0.1157,0.0012</t>
+  </si>
+  <si>
+    <t>0.1636,0.0508,0.8224,0.0166</t>
+  </si>
+  <si>
+    <t>0.9078,0.0191,0.1072,0.0019</t>
+  </si>
+  <si>
+    <t>0.0377,0.9576,0.0189,0.0026</t>
+  </si>
+  <si>
+    <t>0.0190,0.9665,0.0347,0.0016</t>
+  </si>
+  <si>
+    <t>0.4385,0.6830,0.0075,0.0020</t>
+  </si>
+  <si>
+    <t>0.1169,0.9103,0.0066,0.0006</t>
+  </si>
+  <si>
+    <t>0.0108,0.9794,0.0263,0.0004</t>
+  </si>
+  <si>
+    <t>0.8715,0.0148,0.0843,0.0283</t>
+  </si>
+  <si>
+    <t>0.8736,0.0096,0.2074,0.0028</t>
+  </si>
+  <si>
+    <t>0.0461,0.2043,0.8228,0.0846</t>
+  </si>
+  <si>
+    <t>0.2900,0.1071,0.6449,0.0174</t>
+  </si>
+  <si>
+    <t>0.1639,0.0323,0.8570,0.0058</t>
+  </si>
+  <si>
+    <t>0.1919,0.5387,0.3859,0.1699</t>
+  </si>
+  <si>
+    <t>0.2544,0.0166,0.8160,0.0092</t>
+  </si>
+  <si>
+    <t>0.1212,0.8473,0.0312,0.0006</t>
+  </si>
+  <si>
+    <t>0.6253,0.2444,0.2433,0.0524</t>
+  </si>
+  <si>
+    <t>0.0009,0.0030,0.9826,0.0442</t>
+  </si>
+  <si>
+    <t>0.0133,0.8062,0.5352,0.0009</t>
+  </si>
+  <si>
+    <t>0.5605,0.4299,0.0551,0.0782</t>
+  </si>
+  <si>
+    <t>0.8233,0.1077,0.0644,0.0213</t>
+  </si>
+  <si>
+    <t>0.5753,0.4175,0.0229,0.0006</t>
+  </si>
+  <si>
+    <t>0.0044,0.9332,0.7600,0.0005</t>
+  </si>
+  <si>
+    <t>0.0322,0.9046,0.0821,0.0140</t>
+  </si>
+  <si>
+    <t>0.7257,0.0065,0.0846,0.1254</t>
+  </si>
+  <si>
+    <t>0.3949,0.2050,0.5049,0.1047</t>
+  </si>
+  <si>
+    <t>0.6923,0.0195,0.1003,0.1642</t>
+  </si>
+  <si>
+    <t>0.0322,0.3908,0.8702,0.0022</t>
+  </si>
+  <si>
+    <t>0.0114,0.9809,0.0143,0.0007</t>
+  </si>
+  <si>
+    <t>0.0507,0.3609,0.7638,0.0063</t>
+  </si>
+  <si>
+    <t>0.8803,0.0191,0.0491,0.0667</t>
+  </si>
+  <si>
+    <t>0.0070,0.9888,0.0071,0.0010</t>
+  </si>
+  <si>
+    <t>0.0045,0.9899,0.0098,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.9967,0.0171,0.0000</t>
+  </si>
+  <si>
+    <t>0.1298,0.3696,0.7031,0.0476</t>
+  </si>
+  <si>
+    <t>0.0767,0.3440,0.8593,0.0060</t>
+  </si>
+  <si>
+    <t>0.2389,0.0402,0.7717,0.0168</t>
+  </si>
+  <si>
+    <t>0.0341,0.0521,0.9172,0.0464</t>
+  </si>
+  <si>
+    <t>0.0342,0.1760,0.9250,0.0106</t>
+  </si>
+  <si>
+    <t>0.0558,0.0859,0.8955,0.0149</t>
+  </si>
+  <si>
+    <t>0.9558,0.0830,0.0025,0.0006</t>
+  </si>
+  <si>
+    <t>0.9741,0.0176,0.0060,0.0046</t>
+  </si>
+  <si>
+    <t>0.9644,0.0346,0.0043,0.0045</t>
+  </si>
+  <si>
+    <t>0.0366,0.0133,0.9160,0.0473</t>
+  </si>
+  <si>
+    <t>0.9915,0.0055,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.9943,0.0040,0.0011,0.0009</t>
+  </si>
+  <si>
+    <t>0.9592,0.0480,0.0078,0.0024</t>
+  </si>
+  <si>
+    <t>0.0164,0.8082,0.8516,0.0044</t>
+  </si>
+  <si>
+    <t>0.0339,0.2939,0.9420,0.0030</t>
+  </si>
+  <si>
+    <t>0.0529,0.1896,0.8508,0.0241</t>
+  </si>
+  <si>
+    <t>0.0103,0.9283,0.5582,0.0017</t>
+  </si>
+  <si>
+    <t>0.0850,0.0677,0.8893,0.0262</t>
+  </si>
+  <si>
+    <t>0.1406,0.8107,0.0666,0.0061</t>
+  </si>
+  <si>
+    <t>0.0282,0.9852,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.7974,0.0351,0.3270,0.0054</t>
+  </si>
+  <si>
+    <t>0.8278,0.0680,0.1507,0.0112</t>
+  </si>
+  <si>
+    <t>0.0188,0.0468,0.9697,0.0046</t>
+  </si>
+  <si>
+    <t>0.0115,0.6111,0.8688,0.0017</t>
+  </si>
+  <si>
+    <t>0.0081,0.8948,0.5893,0.0015</t>
+  </si>
+  <si>
+    <t>0.0041,0.9890,0.0232,0.0004</t>
+  </si>
+  <si>
+    <t>0.0080,0.9278,0.4976,0.0015</t>
+  </si>
+  <si>
+    <t>0.0322,0.0036,0.0077,0.9790</t>
+  </si>
+  <si>
+    <t>0.0227,0.0047,0.0024,0.9863</t>
+  </si>
+  <si>
+    <t>0.0494,0.0071,0.0026,0.9744</t>
+  </si>
+  <si>
+    <t>0.1263,0.0032,0.0105,0.9149</t>
+  </si>
+  <si>
+    <t>0.0084,0.0012,0.0009,0.9949</t>
+  </si>
+  <si>
+    <t>0.0270,0.0100,0.0023,0.9832</t>
+  </si>
+  <si>
+    <t>0.0010,0.9604,0.7857,0.0001</t>
+  </si>
+  <si>
+    <t>0.0078,0.8560,0.8676,0.0034</t>
+  </si>
+  <si>
+    <t>0.0405,0.5836,0.7625,0.0083</t>
+  </si>
+  <si>
+    <t>0.1554,0.4478,0.5525,0.0471</t>
+  </si>
+  <si>
+    <t>0.0013,0.9713,0.6145,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.9529,0.2502,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0007,0.0003,0.0013</t>
+  </si>
+  <si>
+    <t>0.9803,0.0231,0.0044,0.0021</t>
+  </si>
+  <si>
+    <t>0.9731,0.0278,0.0064,0.0034</t>
+  </si>
+  <si>
+    <t>0.9503,0.0758,0.0069,0.0021</t>
+  </si>
+  <si>
+    <t>0.9864,0.0133,0.0021,0.0008</t>
+  </si>
+  <si>
+    <t>0.9970,0.0017,0.0003,0.0005</t>
+  </si>
+  <si>
+    <t>0.9920,0.0048,0.0016,0.0014</t>
+  </si>
+  <si>
+    <t>0.9929,0.0063,0.0022,0.0004</t>
+  </si>
+  <si>
+    <t>0.9951,0.0027,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9978,0.0014,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.9987,0.0006,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9962,0.0026,0.0012,0.0004</t>
+  </si>
+  <si>
+    <t>0.9850,0.0168,0.0037,0.0011</t>
+  </si>
+  <si>
+    <t>0.9947,0.0018,0.0015,0.0019</t>
+  </si>
+  <si>
+    <t>0.9974,0.0011,0.0006,0.0005</t>
+  </si>
+  <si>
+    <t>0.0953,0.0048,0.8969,0.0227</t>
+  </si>
+  <si>
+    <t>0.1448,0.2145,0.7534,0.0119</t>
+  </si>
+  <si>
+    <t>0.9504,0.0086,0.0308,0.0067</t>
+  </si>
+  <si>
+    <t>0.0496,0.0584,0.9149,0.0093</t>
+  </si>
+  <si>
+    <t>0.1442,0.8712,0.0122,0.0012</t>
+  </si>
+  <si>
+    <t>0.0422,0.9401,0.0214,0.0024</t>
+  </si>
+  <si>
+    <t>0.3251,0.7805,0.0098,0.0033</t>
+  </si>
+  <si>
+    <t>0.2363,0.8416,0.0082,0.0011</t>
+  </si>
+  <si>
+    <t>0.1388,0.8619,0.0187,0.0015</t>
+  </si>
+  <si>
+    <t>0.0223,0.9635,0.0155,0.0005</t>
+  </si>
+  <si>
+    <t>0.5059,0.6322,0.0084,0.0010</t>
+  </si>
+  <si>
+    <t>0.6816,0.2303,0.0905,0.0066</t>
+  </si>
+  <si>
+    <t>0.6531,0.0226,0.4271,0.0198</t>
+  </si>
+  <si>
+    <t>0.0838,0.8243,0.1406,0.1528</t>
+  </si>
+  <si>
+    <t>0.5343,0.0776,0.4070,0.0384</t>
+  </si>
+  <si>
+    <t>0.6624,0.1888,0.2363,0.1129</t>
+  </si>
+  <si>
+    <t>0.0043,0.9918,0.0080,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.9963,0.0016,0.0001</t>
+  </si>
+  <si>
+    <t>0.0055,0.9822,0.0673,0.0037</t>
+  </si>
+  <si>
+    <t>0.0022,0.9776,0.1820,0.0002</t>
+  </si>
+  <si>
+    <t>0.0363,0.9395,0.0758,0.0003</t>
+  </si>
+  <si>
+    <t>0.7419,0.1348,0.1233,0.0022</t>
+  </si>
+  <si>
+    <t>0.7995,0.1371,0.0562,0.0017</t>
+  </si>
+  <si>
+    <t>0.9840,0.0097,0.0073,0.0029</t>
+  </si>
+  <si>
+    <t>0.9900,0.0043,0.0044,0.0025</t>
+  </si>
+  <si>
+    <t>0.9957,0.0023,0.0006,0.0009</t>
+  </si>
+  <si>
+    <t>0.9645,0.0202,0.0178,0.0083</t>
+  </si>
+  <si>
+    <t>0.9964,0.0013,0.0005,0.0012</t>
+  </si>
+  <si>
+    <t>0.9930,0.0049,0.0039,0.0005</t>
+  </si>
+  <si>
+    <t>0.9900,0.0030,0.0034,0.0034</t>
+  </si>
+  <si>
+    <t>0.9884,0.0020,0.0029,0.0050</t>
+  </si>
+  <si>
+    <t>0.0142,0.7923,0.6231,0.0015</t>
+  </si>
+  <si>
+    <t>0.0031,0.9004,0.8466,0.0008</t>
+  </si>
+  <si>
+    <t>0.0355,0.3408,0.8098,0.0033</t>
+  </si>
+  <si>
+    <t>0.1191,0.3107,0.7620,0.0129</t>
+  </si>
+  <si>
+    <t>0.7645,0.1150,0.0110,0.0874</t>
+  </si>
+  <si>
+    <t>0.8457,0.0542,0.0761,0.0201</t>
+  </si>
+  <si>
+    <t>0.8640,0.0065,0.2471,0.0031</t>
+  </si>
+  <si>
+    <t>0.6724,0.0743,0.3832,0.0278</t>
+  </si>
+  <si>
+    <t>0.1640,0.0033,0.0044,0.9093</t>
+  </si>
+  <si>
+    <t>0.0014,0.0015,0.0004,0.9986</t>
+  </si>
+  <si>
+    <t>0.0136,0.0012,0.0010,0.9932</t>
+  </si>
+  <si>
+    <t>0.0184,0.0002,0.0005,0.9925</t>
+  </si>
+  <si>
+    <t>0.0027,0.9772,0.0751,0.0033</t>
+  </si>
+  <si>
+    <t>0.9710,0.0244,0.0033,0.0047</t>
+  </si>
+  <si>
+    <t>0.2038,0.7586,0.0578,0.0911</t>
+  </si>
+  <si>
+    <t>0.9893,0.0080,0.0030,0.0009</t>
+  </si>
+  <si>
+    <t>0.5744,0.4692,0.0431,0.0086</t>
+  </si>
+  <si>
+    <t>0.9930,0.0026,0.0013,0.0014</t>
+  </si>
+  <si>
+    <t>0.2156,0.0125,0.0654,0.7504</t>
+  </si>
+  <si>
+    <t>0.8922,0.0552,0.0174,0.0526</t>
+  </si>
+  <si>
+    <t>0.0166,0.0213,0.9026,0.1208</t>
+  </si>
+  <si>
+    <t>0.9370,0.0020,0.0139,0.0346</t>
+  </si>
+  <si>
+    <t>0.8641,0.0238,0.0291,0.0870</t>
+  </si>
+  <si>
+    <t>0.7560,0.1594,0.0850,0.0035</t>
+  </si>
+  <si>
+    <t>0.9255,0.0615,0.0040,0.0133</t>
+  </si>
+  <si>
+    <t>0.9353,0.0482,0.0233,0.0018</t>
+  </si>
+  <si>
+    <t>0.1949,0.6825,0.1478,0.0055</t>
+  </si>
+  <si>
+    <t>0.3505,0.2627,0.3746,0.0090</t>
+  </si>
+  <si>
+    <t>0.6234,0.4801,0.0200,0.0056</t>
+  </si>
+  <si>
+    <t>0.9830,0.0041,0.0040,0.0094</t>
+  </si>
+  <si>
+    <t>0.9916,0.0061,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9942,0.0022,0.0014,0.0016</t>
+  </si>
+  <si>
+    <t>0.9880,0.0023,0.0019,0.0068</t>
+  </si>
+  <si>
+    <t>0.9968,0.0011,0.0014,0.0006</t>
+  </si>
+  <si>
+    <t>0.9946,0.0031,0.0017,0.0005</t>
+  </si>
+  <si>
+    <t>0.9781,0.0110,0.0018,0.0078</t>
+  </si>
+  <si>
+    <t>0.9936,0.0006,0.0002,0.0037</t>
+  </si>
+  <si>
+    <t>0.7657,0.4418,0.0025,0.0004</t>
+  </si>
+  <si>
+    <t>0.6162,0.3648,0.0573,0.0067</t>
+  </si>
+  <si>
+    <t>0.2394,0.7203,0.0616,0.0067</t>
+  </si>
+  <si>
+    <t>0.4638,0.2311,0.4972,0.0470</t>
+  </si>
+  <si>
+    <t>0.9628,0.0384,0.0089,0.0021</t>
+  </si>
+  <si>
+    <t>0.9331,0.0456,0.0215,0.0109</t>
+  </si>
+  <si>
+    <t>0.9917,0.0063,0.0019,0.0010</t>
+  </si>
+  <si>
+    <t>0.9672,0.0267,0.0059,0.0058</t>
+  </si>
+  <si>
+    <t>0.0019,0.1726,0.9877,0.0023</t>
+  </si>
+  <si>
+    <t>0.9780,0.0247,0.0038,0.0015</t>
+  </si>
+  <si>
+    <t>0.0246,0.0704,0.9329,0.0216</t>
+  </si>
+  <si>
+    <t>0.0994,0.3161,0.6867,0.1037</t>
+  </si>
+  <si>
+    <t>0.2669,0.1850,0.6143,0.0467</t>
+  </si>
+  <si>
+    <t>0.0108,0.1718,0.9618,0.0139</t>
+  </si>
+  <si>
+    <t>0.0188,0.1161,0.9508,0.0049</t>
+  </si>
+  <si>
+    <t>0.2546,0.0109,0.8139,0.0118</t>
+  </si>
+  <si>
+    <t>0.0785,0.0642,0.8684,0.0439</t>
+  </si>
+  <si>
+    <t>0.1522,0.3864,0.5417,0.0144</t>
+  </si>
+  <si>
+    <t>0.2369,0.1232,0.7045,0.0145</t>
+  </si>
+  <si>
+    <t>0.3207,0.2534,0.4164,0.0086</t>
+  </si>
+  <si>
+    <t>0.1293,0.4002,0.4899,0.0037</t>
+  </si>
+  <si>
+    <t>0.0371,0.6905,0.5021,0.0024</t>
+  </si>
+  <si>
+    <t>0.7116,0.0945,0.2308,0.0101</t>
+  </si>
+  <si>
+    <t>0.5394,0.3146,0.2312,0.0546</t>
+  </si>
+  <si>
+    <t>0.5055,0.0919,0.4626,0.0504</t>
+  </si>
+  <si>
+    <t>0.9674,0.0579,0.0019,0.0003</t>
+  </si>
+  <si>
+    <t>0.8580,0.1787,0.0113,0.0006</t>
+  </si>
+  <si>
+    <t>0.9621,0.0518,0.0049,0.0010</t>
+  </si>
+  <si>
+    <t>0.9637,0.0599,0.0028,0.0009</t>
+  </si>
+  <si>
+    <t>0.9072,0.1592,0.0059,0.0025</t>
+  </si>
+  <si>
+    <t>0.8748,0.0289,0.1022,0.0032</t>
+  </si>
+  <si>
+    <t>0.8233,0.0446,0.1913,0.0096</t>
+  </si>
+  <si>
+    <t>0.8238,0.0186,0.1615,0.0208</t>
+  </si>
+  <si>
+    <t>0.7690,0.0246,0.3039,0.0053</t>
+  </si>
+  <si>
+    <t>0.6215,0.0542,0.2983,0.0903</t>
+  </si>
+  <si>
+    <t>0.2973,0.0271,0.6428,0.0639</t>
+  </si>
+  <si>
+    <t>0.2098,0.3543,0.5221,0.0181</t>
+  </si>
+  <si>
+    <t>0.1834,0.3030,0.1281,0.6401</t>
+  </si>
+  <si>
+    <t>0.8689,0.0069,0.1899,0.0041</t>
+  </si>
+  <si>
+    <t>0.1376,0.3608,0.5228,0.0156</t>
+  </si>
+  <si>
+    <t>0.9765,0.0192,0.0045,0.0038</t>
+  </si>
+  <si>
+    <t>0.9868,0.0164,0.0022,0.0010</t>
+  </si>
+  <si>
+    <t>0.9862,0.0126,0.0050,0.0013</t>
+  </si>
+  <si>
+    <t>0.9815,0.0200,0.0037,0.0011</t>
+  </si>
+  <si>
+    <t>0.9866,0.0080,0.0037,0.0032</t>
+  </si>
+  <si>
+    <t>0.9890,0.0098,0.0021,0.0010</t>
+  </si>
+  <si>
+    <t>0.9805,0.0190,0.0015,0.0028</t>
+  </si>
+  <si>
+    <t>0.9902,0.0058,0.0032,0.0019</t>
+  </si>
+  <si>
+    <t>0.0244,0.0720,0.9462,0.0112</t>
+  </si>
+  <si>
+    <t>0.2327,0.1869,0.6656,0.0099</t>
+  </si>
+  <si>
+    <t>0.9285,0.0559,0.0198,0.0089</t>
+  </si>
+  <si>
+    <t>0.0495,0.0226,0.9586,0.0035</t>
+  </si>
+  <si>
+    <t>0.0246,0.0330,0.9129,0.0676</t>
+  </si>
+  <si>
+    <t>0.0273,0.5423,0.8098,0.0083</t>
+  </si>
+  <si>
+    <t>0.2100,0.0095,0.8904,0.0008</t>
+  </si>
+  <si>
+    <t>0.1501,0.1102,0.7481,0.0047</t>
+  </si>
+  <si>
+    <t>0.0510,0.0039,0.8850,0.0402</t>
+  </si>
+  <si>
+    <t>0.0999,0.5658,0.3893,0.1244</t>
+  </si>
+  <si>
+    <t>0.2993,0.4081,0.2997,0.0225</t>
+  </si>
+  <si>
+    <t>0.6940,0.0409,0.3118,0.0449</t>
+  </si>
+  <si>
+    <t>0.9293,0.0061,0.0735,0.0055</t>
+  </si>
+  <si>
+    <t>0.9227,0.0140,0.0453,0.0181</t>
+  </si>
+  <si>
+    <t>0.9804,0.0281,0.0023,0.0012</t>
+  </si>
+  <si>
+    <t>0.9925,0.0051,0.0016,0.0010</t>
+  </si>
+  <si>
+    <t>0.9942,0.0033,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.9919,0.0064,0.0034,0.0003</t>
+  </si>
+  <si>
+    <t>0.9969,0.0016,0.0007,0.0005</t>
+  </si>
+  <si>
+    <t>0.9659,0.0399,0.0067,0.0017</t>
+  </si>
+  <si>
+    <t>0.9860,0.0144,0.0023,0.0014</t>
+  </si>
+  <si>
+    <t>0.9927,0.0055,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.1186,0.4151,0.5621,0.0127</t>
+  </si>
+  <si>
+    <t>0.0240,0.4504,0.8926,0.0080</t>
+  </si>
+  <si>
+    <t>0.0715,0.3132,0.7792,0.0283</t>
+  </si>
+  <si>
+    <t>0.6106,0.1478,0.2538,0.0323</t>
+  </si>
+  <si>
+    <t>0.0785,0.0110,0.9262,0.0122</t>
+  </si>
+  <si>
+    <t>0.3911,0.2479,0.2371,0.3978</t>
+  </si>
+  <si>
+    <t>0.5811,0.1056,0.3808,0.0505</t>
+  </si>
+  <si>
+    <t>0.6777,0.0153,0.3557,0.0305</t>
+  </si>
+  <si>
+    <t>0.2212,0.0059,0.0056,0.8739</t>
+  </si>
+  <si>
+    <t>0.4681,0.0062,0.0061,0.6873</t>
+  </si>
+  <si>
+    <t>0.0675,0.0028,0.0019,0.9692</t>
+  </si>
+  <si>
+    <t>0.0088,0.0003,0.0012,0.9950</t>
+  </si>
+  <si>
+    <t>0.0247,0.0004,0.0010,0.9880</t>
+  </si>
+  <si>
+    <t>0.8829,0.0123,0.0348,0.0833</t>
   </si>
 </sst>
 </file>
@@ -1953,10 +1956,10 @@
         <v>259</v>
       </c>
       <c r="C2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1967,10 +1970,10 @@
         <v>260</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1984,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1995,10 +1998,10 @@
         <v>260</v>
       </c>
       <c r="C5" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2015,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2029,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2043,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2057,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2065,10 +2068,10 @@
         <v>259</v>
       </c>
       <c r="C10" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2085,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2099,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2113,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2124,7 +2127,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2135,10 +2138,10 @@
         <v>261</v>
       </c>
       <c r="C15" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2155,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2163,10 +2166,10 @@
         <v>261</v>
       </c>
       <c r="C17" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2180,7 +2183,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2197,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2211,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2225,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2239,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2253,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2267,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2281,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2289,10 +2292,10 @@
         <v>261</v>
       </c>
       <c r="C26" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2303,10 +2306,10 @@
         <v>261</v>
       </c>
       <c r="C27" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2317,10 +2320,10 @@
         <v>261</v>
       </c>
       <c r="C28" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2331,10 +2334,10 @@
         <v>261</v>
       </c>
       <c r="C29" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2345,10 +2348,10 @@
         <v>261</v>
       </c>
       <c r="C30" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2365,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2379,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2393,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2404,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2421,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2435,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2446,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2457,10 +2460,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2474,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2491,7 @@
         <v>259</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2499,10 +2502,10 @@
         <v>261</v>
       </c>
       <c r="C41" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2519,7 @@
         <v>259</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2527,10 +2530,10 @@
         <v>263</v>
       </c>
       <c r="C43" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2547,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2555,10 +2558,10 @@
         <v>261</v>
       </c>
       <c r="C45" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2572,7 +2575,7 @@
         <v>259</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2589,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2603,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2617,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2631,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2639,10 +2642,10 @@
         <v>261</v>
       </c>
       <c r="C51" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2653,10 +2656,10 @@
         <v>261</v>
       </c>
       <c r="C52" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2667,10 +2670,10 @@
         <v>261</v>
       </c>
       <c r="C53" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2681,10 +2684,10 @@
         <v>261</v>
       </c>
       <c r="C54" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2695,10 +2698,10 @@
         <v>261</v>
       </c>
       <c r="C55" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2709,10 +2712,10 @@
         <v>259</v>
       </c>
       <c r="C56" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2723,10 +2726,10 @@
         <v>259</v>
       </c>
       <c r="C57" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2737,10 +2740,10 @@
         <v>259</v>
       </c>
       <c r="C58" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2751,10 +2754,10 @@
         <v>261</v>
       </c>
       <c r="C59" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2771,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2785,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2793,10 +2796,10 @@
         <v>259</v>
       </c>
       <c r="C62" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2813,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2821,10 +2824,10 @@
         <v>261</v>
       </c>
       <c r="C64" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2835,10 +2838,10 @@
         <v>261</v>
       </c>
       <c r="C65" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2855,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2869,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2877,10 +2880,10 @@
         <v>262</v>
       </c>
       <c r="C68" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2897,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2911,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2922,7 +2925,7 @@
         <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2933,10 +2936,10 @@
         <v>261</v>
       </c>
       <c r="C72" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2950,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2964,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2981,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +2995,7 @@
         <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3003,10 +3006,10 @@
         <v>260</v>
       </c>
       <c r="C77" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3017,10 +3020,10 @@
         <v>260</v>
       </c>
       <c r="C78" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3031,10 +3034,10 @@
         <v>260</v>
       </c>
       <c r="C79" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3045,10 +3048,10 @@
         <v>260</v>
       </c>
       <c r="C80" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3059,10 +3062,10 @@
         <v>260</v>
       </c>
       <c r="C81" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3073,10 +3076,10 @@
         <v>260</v>
       </c>
       <c r="C82" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3093,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3107,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3118,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3129,10 +3132,10 @@
         <v>263</v>
       </c>
       <c r="C86" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3149,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3163,7 @@
         <v>262</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3177,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3191,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3199,10 +3202,10 @@
         <v>259</v>
       </c>
       <c r="C91" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3213,10 +3216,10 @@
         <v>259</v>
       </c>
       <c r="C92" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3227,10 +3230,10 @@
         <v>259</v>
       </c>
       <c r="C93" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3241,10 +3244,10 @@
         <v>259</v>
       </c>
       <c r="C94" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3255,10 +3258,10 @@
         <v>259</v>
       </c>
       <c r="C95" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3269,10 +3272,10 @@
         <v>259</v>
       </c>
       <c r="C96" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3289,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3297,10 +3300,10 @@
         <v>259</v>
       </c>
       <c r="C98" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3311,10 +3314,10 @@
         <v>259</v>
       </c>
       <c r="C99" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3331,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3339,10 +3342,10 @@
         <v>259</v>
       </c>
       <c r="C101" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3353,10 +3356,10 @@
         <v>259</v>
       </c>
       <c r="C102" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3373,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3387,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3401,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3409,10 +3412,10 @@
         <v>261</v>
       </c>
       <c r="C106" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3429,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3437,10 +3440,10 @@
         <v>261</v>
       </c>
       <c r="C108" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3457,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3471,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3485,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3499,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3513,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3527,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3538,7 +3541,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3552,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3569,7 @@
         <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3583,7 @@
         <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3594,7 +3597,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3611,7 @@
         <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3625,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3639,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3653,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3667,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3681,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3692,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3706,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3723,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3737,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3745,10 +3748,10 @@
         <v>259</v>
       </c>
       <c r="C130" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3765,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3779,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3793,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3807,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3815,10 +3818,10 @@
         <v>259</v>
       </c>
       <c r="C135" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3832,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3849,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3860,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3871,10 +3874,10 @@
         <v>261</v>
       </c>
       <c r="C139" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3888,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3905,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3919,7 @@
         <v>259</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3933,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3941,10 +3944,10 @@
         <v>260</v>
       </c>
       <c r="C144" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3955,10 +3958,10 @@
         <v>260</v>
       </c>
       <c r="C145" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3969,10 +3972,10 @@
         <v>260</v>
       </c>
       <c r="C146" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3983,10 +3986,10 @@
         <v>260</v>
       </c>
       <c r="C147" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3997,10 +4000,10 @@
         <v>263</v>
       </c>
       <c r="C148" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4011,10 +4014,10 @@
         <v>259</v>
       </c>
       <c r="C149" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4028,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4039,10 +4042,10 @@
         <v>259</v>
       </c>
       <c r="C151" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4053,10 +4056,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4073,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4084,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4095,10 +4098,10 @@
         <v>259</v>
       </c>
       <c r="C155" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4109,10 +4112,10 @@
         <v>261</v>
       </c>
       <c r="C156" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4126,7 +4129,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4143,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4154,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4171,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4182,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4199,7 @@
         <v>262</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4207,10 +4210,10 @@
         <v>259</v>
       </c>
       <c r="C163" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4227,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4235,10 +4238,10 @@
         <v>259</v>
       </c>
       <c r="C165" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4255,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4263,10 +4266,10 @@
         <v>259</v>
       </c>
       <c r="C167" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4283,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4297,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4305,10 +4308,10 @@
         <v>259</v>
       </c>
       <c r="C170" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4319,10 +4322,10 @@
         <v>259</v>
       </c>
       <c r="C171" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4333,10 +4336,10 @@
         <v>259</v>
       </c>
       <c r="C172" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4350,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4361,10 +4364,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4378,7 +4381,7 @@
         <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4392,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4403,10 +4406,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4423,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4431,10 +4434,10 @@
         <v>259</v>
       </c>
       <c r="C179" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4445,10 +4448,10 @@
         <v>259</v>
       </c>
       <c r="C180" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4459,10 +4462,10 @@
         <v>261</v>
       </c>
       <c r="C181" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4473,10 +4476,10 @@
         <v>259</v>
       </c>
       <c r="C182" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4487,10 +4490,10 @@
         <v>261</v>
       </c>
       <c r="C183" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4501,10 +4504,10 @@
         <v>261</v>
       </c>
       <c r="C184" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4515,10 +4518,10 @@
         <v>261</v>
       </c>
       <c r="C185" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4529,10 +4532,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4543,10 +4546,10 @@
         <v>261</v>
       </c>
       <c r="C187" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4557,10 +4560,10 @@
         <v>261</v>
       </c>
       <c r="C188" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4571,10 +4574,10 @@
         <v>261</v>
       </c>
       <c r="C189" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4588,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4599,10 +4602,10 @@
         <v>259</v>
       </c>
       <c r="C191" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4616,7 +4619,7 @@
         <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4627,10 +4630,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4641,10 +4644,10 @@
         <v>261</v>
       </c>
       <c r="C194" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4658,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4675,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4683,10 +4686,10 @@
         <v>259</v>
       </c>
       <c r="C197" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4700,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4711,10 +4714,10 @@
         <v>262</v>
       </c>
       <c r="C199" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4725,10 +4728,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4739,10 +4742,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4759,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4773,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4787,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4801,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4815,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4829,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4837,10 +4840,10 @@
         <v>261</v>
       </c>
       <c r="C208" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4851,10 +4854,10 @@
         <v>261</v>
       </c>
       <c r="C209" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4868,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4885,7 @@
         <v>259</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4899,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4907,10 +4910,10 @@
         <v>259</v>
       </c>
       <c r="C213" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4921,10 +4924,10 @@
         <v>259</v>
       </c>
       <c r="C214" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4935,10 +4938,10 @@
         <v>259</v>
       </c>
       <c r="C215" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4949,10 +4952,10 @@
         <v>259</v>
       </c>
       <c r="C216" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4969,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4977,10 +4980,10 @@
         <v>259</v>
       </c>
       <c r="C218" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4991,10 +4994,10 @@
         <v>259</v>
       </c>
       <c r="C219" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5005,10 +5008,10 @@
         <v>259</v>
       </c>
       <c r="C220" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5019,10 +5022,10 @@
         <v>261</v>
       </c>
       <c r="C221" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5036,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5053,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5061,10 +5064,10 @@
         <v>261</v>
       </c>
       <c r="C224" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5081,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5089,10 +5092,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5109,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5117,10 +5120,10 @@
         <v>261</v>
       </c>
       <c r="C228" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5137,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5145,10 +5148,10 @@
         <v>261</v>
       </c>
       <c r="C230" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5162,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5179,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5193,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5207,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5215,10 +5218,10 @@
         <v>259</v>
       </c>
       <c r="C235" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5229,10 +5232,10 @@
         <v>259</v>
       </c>
       <c r="C236" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5243,10 +5246,10 @@
         <v>259</v>
       </c>
       <c r="C237" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5263,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5271,10 +5274,10 @@
         <v>259</v>
       </c>
       <c r="C239" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5291,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5305,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5319,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5327,10 +5330,10 @@
         <v>261</v>
       </c>
       <c r="C243" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5341,10 +5344,10 @@
         <v>261</v>
       </c>
       <c r="C244" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5355,10 +5358,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5375,7 @@
         <v>259</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5383,10 +5386,10 @@
         <v>261</v>
       </c>
       <c r="C247" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5403,7 @@
         <v>259</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5417,7 @@
         <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5431,7 @@
         <v>259</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5442,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5453,10 +5456,10 @@
         <v>260</v>
       </c>
       <c r="C252" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5467,10 +5470,10 @@
         <v>260</v>
       </c>
       <c r="C253" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5481,10 +5484,10 @@
         <v>260</v>
       </c>
       <c r="C254" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5495,10 +5498,10 @@
         <v>260</v>
       </c>
       <c r="C255" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5515,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
     </row>
   </sheetData>
